--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C42C902-4E46-4A99-B5AE-602C68254B95}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB67453F-A24C-4E84-B479-BE7660AFF1F4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
-    <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,25 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
-  <si>
-    <t>ruido interno</t>
-  </si>
-  <si>
-    <t>ruido externo</t>
-  </si>
-  <si>
-    <t>ruido ferroviario</t>
-  </si>
-  <si>
-    <t>ruido aeronautico</t>
-  </si>
-  <si>
-    <t>ruido interno 10152</t>
-  </si>
-  <si>
-    <t>solicitei campo de fachada</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -199,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -221,12 +202,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,47 +536,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AF6A2D-0495-4BB5-A527-58125004C2DD}">
-  <dimension ref="D5:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -613,97 +547,97 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="9" t="s">
-        <v>22</v>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -722,7 +656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74AA8FCB-3663-445A-9945-CAE71C4AAE1F}">
   <dimension ref="E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -732,7 +666,7 @@
   <sheetData>
     <row r="5" spans="5:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="E5" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB67453F-A24C-4E84-B479-BE7660AFF1F4}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F5D6088-A014-442F-9337-717A8FE22EE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
+    <sheet name="Padrão" sheetId="2" r:id="rId1"/>
     <sheet name="Planilha3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -116,6 +116,106 @@
 •	Ar Interno (MQAI)
 6.	Já selecionar em “Tipo de Monitoramento”: Outro quando os escopos forem
 •	Outros</t>
+  </si>
+  <si>
+    <t>Subtipo do monitoramento</t>
+  </si>
+  <si>
+    <t>Ambiente Externo</t>
+  </si>
+  <si>
+    <t>Ambiente Interno 10151</t>
+  </si>
+  <si>
+    <t>Ambiente Interno 10152</t>
+  </si>
+  <si>
+    <t>Aeronáutico</t>
+  </si>
+  <si>
+    <t>Ferroviário</t>
+  </si>
+  <si>
+    <t>ROMANEIO</t>
+  </si>
+  <si>
+    <t>**Checklist de Saída para Monitoramento de Ruído**
+**1. Antes de sair do laboratório**
+* Ordem de Serviço (OS) avaliada
+* Pontos amostrais identificados
+* Trajeto planejado
+* Acesso ao local confirmado com o cliente
+* EPIs disponíveis e em boas condições
+**2. Equipamentos e insumos**
+**Equipamentos**
+* Sonômetro com calibração válida
+* Calibrador acústico com calibração válida
+* Microfone com calibração válida
+* Termohigroanemômetro com calibração válida
+**Acessórios**
+* Tripé
+* Protetor de vento (windscreen)
+* Trena
+* Maleta/mochila
+**Alimentação e energia**
+* Carregador dos equipamentos
+* Baterias reservas
+* Power bank carregado
+* Celular carregado
+* Carregador do celular
+**3. Itens opcionais para monitoramentos de longa duração**
+* Cabo de extensão
+* Estação meteorológica com calibração válida
+**4. Itens opcionais para monitoramento online**
+* Roteador 4G
+* Internet móvel funcionando
+**5. Verificação final**
+* Equipamentos conferidos
+* Baterias carregadas
+* Materiais acondicionados para transporte
+* Equipe alinhada quanto ao serviço
+* Horário de saída confirmado</t>
+  </si>
+  <si>
+    <t>**🌍 Romaneio para Ensaios de Vibração**
+**1. Antes de sair do laboratório**
+* Ordem de Serviço (OS) avaliada
+* Pontos amostrais identificados
+* Trajeto planejado (chegada com antecedência mínima de 1 hora)
+* Acesso ao local confirmado com o cliente
+* EPIs disponíveis
+**2. Equipamentos e insumos**
+**Equipamentos**
+* Sismógrafo com calibração válida
+* Geofone com calibração válida
+* Microfone com calibração válida
+* Termohigroanemômetro com calibração válida
+**Acessórios**
+* Cabo de conexão entre sismógrafo e geofone
+* Tripé para o microfone
+* Protetor de vento (windscreen)
+* Trena métrica
+* Maleta de transporte
+* Notebook com software SISTEX (confirmar necessidade com o coordenador)
+**Alimentação e energia**
+* Carregador dos equipamentos
+* Baterias reservas
+* Power bank carregado
+* Celular carregado
+* Carregador do celular
+**3. Insumos para fixação do geofone**
+* Cravos para fixação no solo
+* Gesso de secagem rápida
+* Recipiente para preparo do gesso
+* Água para preparo do gesso
+* Fita adesiva (proteção dos furos do geofone)
+* Espátula para remoção do gesso
+**4. Verificação final**
+* Equipamentos conferidos
+* Baterias carregadas
+* Materiais acondicionados para transporte
+* Equipe alinhada quanto ao serviço
+* Horário de saída confirmado</t>
   </si>
 </sst>
 </file>
@@ -180,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -189,19 +289,26 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,15 +644,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.21875" customWidth="1"/>
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -555,102 +664,170 @@
       <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-    </row>
+      <c r="D10" s="1"/>
+      <c r="E10" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -665,7 +842,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="5:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
     </row>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F5D6088-A014-442F-9337-717A8FE22EE3}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977BD2E8-9811-487F-B20E-7DB05721C60E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>ok</t>
-  </si>
-  <si>
-    <t>Substituir "monitorar, preferencialmente, sem pessoas" para "monitorar, preferencialmente, com pessoas"</t>
   </si>
   <si>
     <t>Tipo de Monitoramento</t>
@@ -139,83 +136,49 @@
     <t>ROMANEIO</t>
   </si>
   <si>
-    <t>**Checklist de Saída para Monitoramento de Ruído**
-**1. Antes de sair do laboratório**
-* Ordem de Serviço (OS) avaliada
-* Pontos amostrais identificados
-* Trajeto planejado
-* Acesso ao local confirmado com o cliente
-* EPIs disponíveis e em boas condições
-**2. Equipamentos e insumos**
-**Equipamentos**
-* Sonômetro com calibração válida
-* Calibrador acústico com calibração válida
-* Microfone com calibração válida
-* Termohigroanemômetro com calibração válida
-**Acessórios**
-* Tripé
-* Protetor de vento (windscreen)
-* Trena
-* Maleta/mochila
-**Alimentação e energia**
-* Carregador dos equipamentos
-* Baterias reservas
-* Power bank carregado
-* Celular carregado
-* Carregador do celular
-**3. Itens opcionais para monitoramentos de longa duração**
-* Cabo de extensão
-* Estação meteorológica com calibração válida
-**4. Itens opcionais para monitoramento online**
-* Roteador 4G
-* Internet móvel funcionando
-**5. Verificação final**
-* Equipamentos conferidos
-* Baterias carregadas
-* Materiais acondicionados para transporte
-* Equipe alinhada quanto ao serviço
-* Horário de saída confirmado</t>
-  </si>
-  <si>
-    <t>**🌍 Romaneio para Ensaios de Vibração**
-**1. Antes de sair do laboratório**
-* Ordem de Serviço (OS) avaliada
-* Pontos amostrais identificados
-* Trajeto planejado (chegada com antecedência mínima de 1 hora)
-* Acesso ao local confirmado com o cliente
-* EPIs disponíveis
-**2. Equipamentos e insumos**
-**Equipamentos**
-* Sismógrafo com calibração válida
-* Geofone com calibração válida
-* Microfone com calibração válida
-* Termohigroanemômetro com calibração válida
-**Acessórios**
-* Cabo de conexão entre sismógrafo e geofone
-* Tripé para o microfone
-* Protetor de vento (windscreen)
-* Trena métrica
-* Maleta de transporte
-* Notebook com software SISTEX (confirmar necessidade com o coordenador)
-**Alimentação e energia**
-* Carregador dos equipamentos
-* Baterias reservas
-* Power bank carregado
-* Celular carregado
-* Carregador do celular
-**3. Insumos para fixação do geofone**
-* Cravos para fixação no solo
-* Gesso de secagem rápida
-* Recipiente para preparo do gesso
-* Água para preparo do gesso
-* Fita adesiva (proteção dos furos do geofone)
-* Espátula para remoção do gesso
-**4. Verificação final**
-* Equipamentos conferidos
-* Baterias carregadas
-* Materiais acondicionados para transporte
-* Equipe alinhada quanto ao serviço
-* Horário de saída confirmado</t>
+    <t>Sismografia – NBR 9653</t>
+  </si>
+  <si>
+    <t>Usual</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Patrimônio Espeleológico – CECAV</t>
+  </si>
+  <si>
+    <t>Áreas Habitadas – CETESB DD 215/2007</t>
+  </si>
+  <si>
+    <t>Vibração</t>
+  </si>
+  <si>
+    <t>TELA SERVIÇO (POR PONTO)</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.2 (Vibração)</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.2 (Vibração)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ler documento "ecamp_especificação_docx" item 7.1 </t>
+  </si>
+  <si>
+    <t>OBSERVAÇÕES:</t>
+  </si>
+  <si>
+    <t>Mantenha sempre as alterações e versões que ajustei nas conversas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de referência: </t>
   </si>
 </sst>
 </file>
@@ -253,7 +216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -276,15 +239,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -294,8 +291,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -304,11 +301,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -644,189 +656,375 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="5" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="E3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="16"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="16"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="10" t="s">
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -842,8 +1040,8 @@
   </cols>
   <sheetData>
     <row r="5" spans="5:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="E5" s="4" t="s">
-        <v>17</v>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977BD2E8-9811-487F-B20E-7DB05721C60E}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DE705CC-6453-4ADD-A7A6-9C4CA447EDC0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="39">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>Pátios / Manobras / Cruzamentos</t>
-  </si>
-  <si>
-    <t>ok</t>
   </si>
   <si>
     <t>Tipo de Monitoramento</t>
@@ -157,9 +154,6 @@
     <t>TELA SERVIÇO (POR PONTO)</t>
   </si>
   <si>
-    <t>Ok</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -179,6 +173,12 @@
   </si>
   <si>
     <t xml:space="preserve">Documento de referência: </t>
+  </si>
+  <si>
+    <t>e-CAMP</t>
+  </si>
+  <si>
+    <t>pronto. Não mexer.</t>
   </si>
 </sst>
 </file>
@@ -202,7 +202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +212,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -321,6 +327,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -664,6 +673,7 @@
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
@@ -674,58 +684,61 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2" s="16"/>
-      <c r="G2" t="s">
-        <v>31</v>
+      <c r="G2" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16"/>
-      <c r="G3" t="s">
-        <v>13</v>
+      <c r="G3" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -736,15 +749,18 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4" s="16"/>
+      <c r="G4" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -752,15 +768,18 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="16"/>
+      <c r="G5" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -770,15 +789,18 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="16"/>
+      <c r="G6" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -788,15 +810,18 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7" s="16"/>
+      <c r="G7" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -806,15 +831,18 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" s="16"/>
+      <c r="G8" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
@@ -824,135 +852,144 @@
         <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F9" s="16"/>
+      <c r="G9" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D14" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="F15" s="4" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
@@ -961,68 +998,75 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17" s="11"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
-    </row>
-    <row r="22" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
         <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1085,7 @@
   <sheetData>
     <row r="5" spans="5:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DE705CC-6453-4ADD-A7A6-9C4CA447EDC0}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7852CFC-639C-4E02-89EB-3CB5C2252DE1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -672,7 +672,8 @@
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
-    <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="51.88671875" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -785,7 +786,7 @@
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -806,7 +807,7 @@
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1091,4 +1092,237 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010012D067C7C505F94DA745333F0C70E18C" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a7942e81b10ac3f7052d292e3c7485f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ceff588c-4f4f-49af-b7d7-c9c79415ad32" xmlns:ns3="0ea24c86-fc74-4fa0-a83b-660477924ea4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3596c5fc9896945baf8297a4f7e536bd" ns2:_="" ns3:_="">
+    <xsd:import namespace="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
+    <xsd:import namespace="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ceff588c-4f4f-49af-b7d7-c9c79415ad32" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e9d251d0-a9ed-4942-8f9c-4135f39fc0f0" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="17" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0ea24c86-fc74-4fa0-a83b-660477924ea4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2bd60ddc-46c7-4f89-952c-d01989346355}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0ea24c86-fc74-4fa0-a83b-660477924ea4">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA0AE08-2331-4162-B9EC-E40252058BA9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}"/>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7852CFC-639C-4E02-89EB-3CB5C2252DE1}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A839BED7-ADD2-4BFE-A667-046CD60D8FA6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -286,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -306,13 +306,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -329,6 +325,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -687,7 +686,7 @@
       <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -704,20 +703,20 @@
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="10" t="s">
+      <c r="F2" s="14"/>
+      <c r="G2" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -725,20 +724,20 @@
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -752,14 +751,14 @@
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -767,18 +766,18 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="14"/>
+      <c r="G5" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -786,20 +785,20 @@
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="14"/>
+      <c r="G6" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -807,20 +806,20 @@
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -828,20 +827,20 @@
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="14"/>
+      <c r="G8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -849,25 +848,25 @@
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -876,7 +875,7 @@
       <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -885,19 +884,19 @@
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -906,10 +905,10 @@
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -918,7 +917,7 @@
       <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -927,19 +926,19 @@
       <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -948,10 +947,10 @@
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="10"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -960,7 +959,7 @@
       <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -969,19 +968,19 @@
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -990,69 +989,69 @@
       <c r="F15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="10"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="15"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
@@ -1084,7 +1083,7 @@
     <col min="5" max="5" width="71.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="5:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="5:5" ht="388.8" x14ac:dyDescent="0.3">
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
@@ -1296,15 +1295,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1315,14 +1305,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA0AE08-2331-4162-B9EC-E40252058BA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA0AE08-2331-4162-B9EC-E40252058BA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
+    <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
+    <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A839BED7-ADD2-4BFE-A667-046CD60D8FA6}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77CC868-61AE-48F6-8093-EF5F7321E6FF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="38">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>Mantenha sempre as alterações e versões que ajustei nas conversas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documento de referência: </t>
   </si>
   <si>
     <t>e-CAMP</t>
@@ -286,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -300,34 +297,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -664,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -686,7 +687,7 @@
       <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -696,177 +697,177 @@
         <v>29</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="14"/>
+      <c r="G5" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="F6" s="14"/>
+      <c r="G6" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="14"/>
+      <c r="G7" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="F8" s="14"/>
+      <c r="G8" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E9" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" s="14"/>
-      <c r="G9" s="7" t="s">
-        <v>38</v>
+      <c r="G9" s="15" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -875,7 +876,7 @@
       <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -884,10 +885,10 @@
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -896,7 +897,7 @@
       <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -905,10 +906,10 @@
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="7"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -917,7 +918,7 @@
       <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -926,10 +927,10 @@
       <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -938,7 +939,7 @@
       <c r="C13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -947,10 +948,10 @@
       <c r="F13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="7"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -959,7 +960,7 @@
       <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -968,10 +969,10 @@
       <c r="F14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="7"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -980,7 +981,7 @@
       <c r="C15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -989,84 +990,76 @@
       <c r="F15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
       <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77CC868-61AE-48F6-8093-EF5F7321E6FF}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C1AC69-1DC5-45B2-9253-A930E5DDB77E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Padrão" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="47">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -176,6 +176,33 @@
   </si>
   <si>
     <t>pronto. Não mexer.</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>PM10</t>
+  </si>
+  <si>
+    <t>PM2,5</t>
+  </si>
+  <si>
+    <t>SO2</t>
+  </si>
+  <si>
+    <t>NO2</t>
+  </si>
+  <si>
+    <t>Ozônio (O3)</t>
+  </si>
+  <si>
+    <t>VOC</t>
+  </si>
+  <si>
+    <t>Poeira Sedimentável</t>
+  </si>
+  <si>
+    <t>Monitoramento automático</t>
   </si>
 </sst>
 </file>
@@ -219,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -279,11 +306,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -331,6 +367,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -993,7 +1031,9 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1002,7 +1042,9 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -1011,7 +1053,9 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
+      <c r="A18" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1020,7 +1064,9 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1029,7 +1075,9 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="A20" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1038,7 +1086,9 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+      <c r="A21" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1047,6 +1097,9 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1055,10 +1108,60 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="19"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B28" t="s">
         <v>35</v>
       </c>
     </row>

--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C1AC69-1DC5-45B2-9253-A930E5DDB77E}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE363D00-7F61-4F7A-818F-FF5F6642290B}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Padrão" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -203,6 +203,24 @@
   </si>
   <si>
     <t>Monitoramento automático</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.3.1</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.3.1 Particulados</t>
+  </si>
+  <si>
+    <t>QAR Externo</t>
+  </si>
+  <si>
+    <t>Particulados</t>
+  </si>
+  <si>
+    <t>Gases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ler documento "ecamp_especificação_docx" item 8.3.1 </t>
   </si>
 </sst>
 </file>
@@ -319,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -335,9 +353,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -367,8 +382,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,7 +725,7 @@
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="5" max="5" width="49.88671875" customWidth="1"/>
     <col min="6" max="6" width="51.88671875" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -739,409 +754,472 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="13"/>
+      <c r="G4" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="13"/>
+      <c r="G5" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15" t="s">
+      <c r="F6" s="13"/>
+      <c r="G6" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15" t="s">
+      <c r="F8" s="13"/>
+      <c r="G8" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1391,6 +1469,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1399,15 +1486,6 @@
     <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1430,6 +1508,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1438,12 +1524,4 @@
     <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{168677DE-32DB-4EA7-AD63-4473747FF806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE363D00-7F61-4F7A-818F-FF5F6642290B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AC16B66-2E58-4927-AA28-87A5620058B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="62">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -221,6 +221,33 @@
   </si>
   <si>
     <t xml:space="preserve">Ler documento "ecamp_especificação_docx" item 8.3.1 </t>
+  </si>
+  <si>
+    <t>Fuligem – Escala de Ringelmann</t>
+  </si>
+  <si>
+    <t>Fuligem – Opacímetro</t>
+  </si>
+  <si>
+    <t>Opacidade</t>
+  </si>
+  <si>
+    <t>Ringelmann</t>
+  </si>
+  <si>
+    <t>Opacímetro</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.4.1</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.4.2</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.4.1</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.4.2</t>
   </si>
 </sst>
 </file>
@@ -337,12 +364,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -740,7 +764,7 @@
       <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -754,486 +778,514 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="5"/>
+      <c r="G17" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -1258,7 +1310,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="5:5" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1469,15 +1521,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1486,6 +1529,15 @@
     <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1508,14 +1560,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1524,4 +1568,12 @@
     <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AC16B66-2E58-4927-AA28-87A5620058B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{83E09168-405E-41CC-B314-BC678F77B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1CF8B34-AABF-4C96-A23E-F2943FBFC230}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -248,6 +248,30 @@
   </si>
   <si>
     <t>Ler documento "ecamp_especificação_docx" item 8.4.2</t>
+  </si>
+  <si>
+    <t>Ar Interno (MQAI)</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.5</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.5</t>
+  </si>
+  <si>
+    <t>QAR Interno</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 7.6</t>
+  </si>
+  <si>
+    <t>Ler documento "ecamp_especificação_docx" item 8.6</t>
   </si>
 </sst>
 </file>
@@ -355,7 +379,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -372,14 +398,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -406,8 +428,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -764,7 +788,7 @@
       <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -778,520 +802,558 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="10"/>
+      <c r="G5" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="10"/>
+      <c r="G6" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="10"/>
+      <c r="G9" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
     </row>
     <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
     </row>
     <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="4"/>
+      <c r="G26" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>34</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1521,6 +1583,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1529,15 +1600,6 @@
     <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1560,6 +1622,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1568,12 +1638,4 @@
     <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{83E09168-405E-41CC-B314-BC678F77B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1CF8B34-AABF-4C96-A23E-F2943FBFC230}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{83E09168-405E-41CC-B314-BC678F77B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2289503-A14A-45BF-9721-E330F0207856}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="70">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -295,7 +295,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +311,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -429,9 +435,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1316,38 +1323,37 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="18" t="s">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="9" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="3"/>
+      <c r="G28" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1583,15 +1589,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1600,6 +1597,15 @@
     <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1622,14 +1628,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1638,4 +1636,12 @@
     <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -1589,6 +1589,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
@@ -1597,15 +1606,6 @@
     <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1628,6 +1628,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1636,12 +1644,4 @@
     <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhas/escopo_metodo_os.xlsx
+++ b/planilhas/escopo_metodo_os.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engearlaboratorio.sharepoint.com/sites/EngearFinanceiro/Documentos Compartilhados/FINANCEIRO LAB/0 SISTEMA SGE/E-CAMP/planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{83E09168-405E-41CC-B314-BC678F77B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2289503-A14A-45BF-9721-E330F0207856}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{1C9B1AFB-302F-4587-B0E1-41D79FFD54BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E646704E-541B-48B8-BF4E-5C7F2B7FA7C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9CD6052-B43C-4BA8-A7B7-6CEBB0E5B4CD}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="84">
   <si>
     <t>Ruído Ambiental – NBR 10151</t>
   </si>
@@ -272,6 +272,48 @@
   </si>
   <si>
     <t>Ler documento "ecamp_especificação_docx" item 8.6</t>
+  </si>
+  <si>
+    <t>FOTOS</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de ambientes}</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{método}_{Nº da Revisão}_{Qts de ambientes}</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{método}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{QAR externo}_{Escopo}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Foto}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de veículos}</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{método}_{Nº da Revisão}_{Qts de ambientes}</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{método}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de ambientes}</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{QAR externo}_{Escopo}_{Nº da Revisão}_{Qts de pontos}</t>
+  </si>
+  <si>
+    <t>{Campo}_{OS}_{Projeto}_{Nº da Campanha}_{Escopo}_{Nº da Revisão}_{Qts de veículos}</t>
   </si>
 </sst>
 </file>
@@ -396,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -438,6 +480,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -773,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9526D981-1FA4-46DC-815A-C9E12F5EFA92}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -785,7 +830,7 @@
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +852,14 @@
       <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -828,8 +879,14 @@
       <c r="G2" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -849,8 +906,14 @@
       <c r="G3" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -870,8 +933,14 @@
       <c r="G4" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -889,8 +958,14 @@
       <c r="G5" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
@@ -910,8 +985,14 @@
       <c r="G6" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
@@ -931,8 +1012,14 @@
       <c r="G7" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>10</v>
       </c>
@@ -952,8 +1039,14 @@
       <c r="G8" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>10</v>
       </c>
@@ -973,8 +1066,14 @@
       <c r="G9" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>23</v>
       </c>
@@ -996,8 +1095,14 @@
       <c r="G10" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
@@ -1019,8 +1124,14 @@
       <c r="G11" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -1042,8 +1153,14 @@
       <c r="G12" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -1065,8 +1182,14 @@
       <c r="G13" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -1088,8 +1211,14 @@
       <c r="G14" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -1111,8 +1240,14 @@
       <c r="G15" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>38</v>
       </c>
@@ -1132,8 +1267,14 @@
       <c r="G16" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>39</v>
       </c>
@@ -1153,8 +1294,14 @@
       <c r="G17" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>40</v>
       </c>
@@ -1174,8 +1321,14 @@
       <c r="G18" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -1189,8 +1342,14 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
@@ -1204,8 +1363,14 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1219,8 +1384,14 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
@@ -1234,8 +1405,14 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -1249,8 +1426,14 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -1264,8 +1447,14 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H24" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -1279,8 +1468,14 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H25" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>53</v>
       </c>
@@ -1300,8 +1495,14 @@
       <c r="G26" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>54</v>
       </c>
@@ -1321,8 +1522,14 @@
       <c r="G27" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>62</v>
       </c>
@@ -1340,8 +1547,14 @@
       <c r="G28" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>66</v>
       </c>
@@ -1355,7 +1568,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1388,6 +1601,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010012D067C7C505F94DA745333F0C70E18C" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a7942e81b10ac3f7052d292e3c7485f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ceff588c-4f4f-49af-b7d7-c9c79415ad32" xmlns:ns3="0ea24c86-fc74-4fa0-a83b-660477924ea4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3596c5fc9896945baf8297a4f7e536bd" ns2:_="" ns3:_="">
     <xsd:import namespace="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
@@ -1588,7 +1812,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1597,18 +1821,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ceff588c-4f4f-49af-b7d7-c9c79415ad32">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0ea24c86-fc74-4fa0-a83b-660477924ea4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
+    <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA0AE08-2331-4162-B9EC-E40252058BA9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1627,21 +1851,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5B55AC-A0C1-45C3-9411-3D2F7156D1B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB7D7E8-8145-4A74-B49E-03C8140943AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ceff588c-4f4f-49af-b7d7-c9c79415ad32"/>
-    <ds:schemaRef ds:uri="0ea24c86-fc74-4fa0-a83b-660477924ea4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>